--- a/data_validation/筛选后的数据.xlsx
+++ b/data_validation/筛选后的数据.xlsx
@@ -14,6 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="????_30?" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -486,4 +487,633 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>14.207</v>
+      </c>
+      <c r="B2">
+        <v>7.718</v>
+      </c>
+      <c r="C2">
+        <v>2.534</v>
+      </c>
+      <c r="D2">
+        <v>-0.4</v>
+      </c>
+      <c r="E2">
+        <v>-0.325</v>
+      </c>
+      <c r="F2">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>6.366</v>
+      </c>
+      <c r="B3">
+        <v>7.597</v>
+      </c>
+      <c r="C3">
+        <v>2.495</v>
+      </c>
+      <c r="D3">
+        <v>2.8</v>
+      </c>
+      <c r="E3">
+        <v>-1.1</v>
+      </c>
+      <c r="F3">
+        <v>1.875</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>27.358</v>
+      </c>
+      <c r="B4">
+        <v>9.005</v>
+      </c>
+      <c r="C4">
+        <v>2.525</v>
+      </c>
+      <c r="D4">
+        <v>1.9</v>
+      </c>
+      <c r="E4">
+        <v>1.5</v>
+      </c>
+      <c r="F4">
+        <v>4.275</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>27.299</v>
+      </c>
+      <c r="B5">
+        <v>9.159</v>
+      </c>
+      <c r="C5">
+        <v>2.518</v>
+      </c>
+      <c r="D5">
+        <v>1.175</v>
+      </c>
+      <c r="E5">
+        <v>0.75</v>
+      </c>
+      <c r="F5">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4.43</v>
+      </c>
+      <c r="B6">
+        <v>10.835</v>
+      </c>
+      <c r="C6">
+        <v>2.498</v>
+      </c>
+      <c r="D6">
+        <v>1.275</v>
+      </c>
+      <c r="E6">
+        <v>2.025</v>
+      </c>
+      <c r="F6">
+        <v>3.425</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>24.407</v>
+      </c>
+      <c r="B7">
+        <v>0.663</v>
+      </c>
+      <c r="C7">
+        <v>2.496</v>
+      </c>
+      <c r="D7">
+        <v>-4.275</v>
+      </c>
+      <c r="E7">
+        <v>3.25</v>
+      </c>
+      <c r="F7">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1.221</v>
+      </c>
+      <c r="B8">
+        <v>10.734</v>
+      </c>
+      <c r="C8">
+        <v>2.528</v>
+      </c>
+      <c r="D8">
+        <v>0.325</v>
+      </c>
+      <c r="E8">
+        <v>0.3</v>
+      </c>
+      <c r="F8">
+        <v>2.775</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3.088</v>
+      </c>
+      <c r="B9">
+        <v>8.343</v>
+      </c>
+      <c r="C9">
+        <v>2.5</v>
+      </c>
+      <c r="D9">
+        <v>-3</v>
+      </c>
+      <c r="E9">
+        <v>-1.85</v>
+      </c>
+      <c r="F9">
+        <v>3.575</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>22.916</v>
+      </c>
+      <c r="B10">
+        <v>11.947</v>
+      </c>
+      <c r="C10">
+        <v>2.501</v>
+      </c>
+      <c r="D10">
+        <v>4.8</v>
+      </c>
+      <c r="E10">
+        <v>-9.025</v>
+      </c>
+      <c r="F10">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>20.918</v>
+      </c>
+      <c r="B11">
+        <v>11.749</v>
+      </c>
+      <c r="C11">
+        <v>2.52</v>
+      </c>
+      <c r="D11">
+        <v>0.775</v>
+      </c>
+      <c r="E11">
+        <v>-1.875</v>
+      </c>
+      <c r="F11">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1.817</v>
+      </c>
+      <c r="B12">
+        <v>0.658</v>
+      </c>
+      <c r="C12">
+        <v>2.488</v>
+      </c>
+      <c r="D12">
+        <v>0.45</v>
+      </c>
+      <c r="E12">
+        <v>1.125</v>
+      </c>
+      <c r="F12">
+        <v>2.375</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>3.767</v>
+      </c>
+      <c r="B13">
+        <v>4.736</v>
+      </c>
+      <c r="C13">
+        <v>2.467</v>
+      </c>
+      <c r="D13">
+        <v>-1.025</v>
+      </c>
+      <c r="E13">
+        <v>-0.45</v>
+      </c>
+      <c r="F13">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>27.197</v>
+      </c>
+      <c r="B14">
+        <v>13.055</v>
+      </c>
+      <c r="C14">
+        <v>2.519</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>-1.175</v>
+      </c>
+      <c r="F14">
+        <v>3.925</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>6.426</v>
+      </c>
+      <c r="B15">
+        <v>1.878</v>
+      </c>
+      <c r="C15">
+        <v>2.466</v>
+      </c>
+      <c r="D15">
+        <v>0.3</v>
+      </c>
+      <c r="E15">
+        <v>1.675</v>
+      </c>
+      <c r="F15">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>4.647</v>
+      </c>
+      <c r="B16">
+        <v>7.457</v>
+      </c>
+      <c r="C16">
+        <v>2.502</v>
+      </c>
+      <c r="D16">
+        <v>1.475</v>
+      </c>
+      <c r="E16">
+        <v>-0.325</v>
+      </c>
+      <c r="F16">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>7.619</v>
+      </c>
+      <c r="B17">
+        <v>4.567</v>
+      </c>
+      <c r="C17">
+        <v>2.491</v>
+      </c>
+      <c r="D17">
+        <v>-1.05</v>
+      </c>
+      <c r="E17">
+        <v>3.55</v>
+      </c>
+      <c r="F17">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2.503</v>
+      </c>
+      <c r="B18">
+        <v>14.248</v>
+      </c>
+      <c r="C18">
+        <v>2.485</v>
+      </c>
+      <c r="D18">
+        <v>-0.15</v>
+      </c>
+      <c r="E18">
+        <v>-3.075</v>
+      </c>
+      <c r="F18">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>6.628</v>
+      </c>
+      <c r="B19">
+        <v>13.298</v>
+      </c>
+      <c r="C19">
+        <v>2.47</v>
+      </c>
+      <c r="D19">
+        <v>-1.75</v>
+      </c>
+      <c r="E19">
+        <v>0.825</v>
+      </c>
+      <c r="F19">
+        <v>2.975</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>7.268</v>
+      </c>
+      <c r="B20">
+        <v>8.69</v>
+      </c>
+      <c r="C20">
+        <v>2.482</v>
+      </c>
+      <c r="D20">
+        <v>-1.15</v>
+      </c>
+      <c r="E20">
+        <v>0.775</v>
+      </c>
+      <c r="F20">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>1.564</v>
+      </c>
+      <c r="B21">
+        <v>6.561</v>
+      </c>
+      <c r="C21">
+        <v>2.494</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>1.45</v>
+      </c>
+      <c r="F21">
+        <v>4.375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>5.711</v>
+      </c>
+      <c r="B22">
+        <v>7.721</v>
+      </c>
+      <c r="C22">
+        <v>2.462</v>
+      </c>
+      <c r="D22">
+        <v>-0.55</v>
+      </c>
+      <c r="E22">
+        <v>0.55</v>
+      </c>
+      <c r="F22">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>5.665</v>
+      </c>
+      <c r="B23">
+        <v>7.731</v>
+      </c>
+      <c r="C23">
+        <v>2.505</v>
+      </c>
+      <c r="D23">
+        <v>-1.175</v>
+      </c>
+      <c r="E23">
+        <v>0.45</v>
+      </c>
+      <c r="F23">
+        <v>3.025</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>25.129</v>
+      </c>
+      <c r="B24">
+        <v>9.136</v>
+      </c>
+      <c r="C24">
+        <v>2.486</v>
+      </c>
+      <c r="D24">
+        <v>1.125</v>
+      </c>
+      <c r="E24">
+        <v>-0.275</v>
+      </c>
+      <c r="F24">
+        <v>4.925</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>1.88</v>
+      </c>
+      <c r="B25">
+        <v>7.04</v>
+      </c>
+      <c r="C25">
+        <v>2.496</v>
+      </c>
+      <c r="D25">
+        <v>-1.7</v>
+      </c>
+      <c r="E25">
+        <v>0.05</v>
+      </c>
+      <c r="F25">
+        <v>1.325</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>27.303</v>
+      </c>
+      <c r="B26">
+        <v>0.684</v>
+      </c>
+      <c r="C26">
+        <v>2.473</v>
+      </c>
+      <c r="D26">
+        <v>-0.1</v>
+      </c>
+      <c r="E26">
+        <v>1.8</v>
+      </c>
+      <c r="F26">
+        <v>4.125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26.616</v>
+      </c>
+      <c r="B27">
+        <v>5.639</v>
+      </c>
+      <c r="C27">
+        <v>2.464</v>
+      </c>
+      <c r="D27">
+        <v>-0.375</v>
+      </c>
+      <c r="E27">
+        <v>-2.225</v>
+      </c>
+      <c r="F27">
+        <v>2.425</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>26.599</v>
+      </c>
+      <c r="B28">
+        <v>5.452</v>
+      </c>
+      <c r="C28">
+        <v>2.523</v>
+      </c>
+      <c r="D28">
+        <v>0.525</v>
+      </c>
+      <c r="E28">
+        <v>-1.975</v>
+      </c>
+      <c r="F28">
+        <v>1.325</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>4.756</v>
+      </c>
+      <c r="B29">
+        <v>4.57</v>
+      </c>
+      <c r="C29">
+        <v>2.534</v>
+      </c>
+      <c r="D29">
+        <v>-0.975</v>
+      </c>
+      <c r="E29">
+        <v>1.325</v>
+      </c>
+      <c r="F29">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>5.83</v>
+      </c>
+      <c r="B30">
+        <v>8.349</v>
+      </c>
+      <c r="C30">
+        <v>2.521</v>
+      </c>
+      <c r="D30">
+        <v>0.45</v>
+      </c>
+      <c r="E30">
+        <v>-1.925</v>
+      </c>
+      <c r="F30">
+        <v>2.925</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>5.525</v>
+      </c>
+      <c r="B31">
+        <v>7.767</v>
+      </c>
+      <c r="C31">
+        <v>2.518</v>
+      </c>
+      <c r="D31">
+        <v>-3.9</v>
+      </c>
+      <c r="E31">
+        <v>-0.25</v>
+      </c>
+      <c r="F31">
+        <v>5.825</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>